--- a/results/job_matches_2026-06-15.xlsx
+++ b/results/job_matches_2026-06-15.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer (AWS &amp; Python)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Loftware</t>
+          <t>ValueBase Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.6</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328900ab048cf04d</t>
+          <t>https://www.indeed.com/viewjob?jk=204e1619685f0b7c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Python)</t>
+          <t>Senior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>American Software Solutions INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=204e1619685f0b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0cc4e514cfd3d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Kubernetes Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Software Solutions INC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0cc4e514cfd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-15.xlsx
+++ b/results/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,105 +503,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Kubernetes Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Software Solutions INC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0cc4e514cfd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
+          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Visualization Senior Associate - Home Lending Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>Athena, RDS, Scala, Polars, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6aec0750240018</t>
         </is>
       </c>
     </row>
@@ -643,35 +643,140 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>GCP Solution Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Senior Solution Developer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c823da42c3926a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-15.xlsx
+++ b/results/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Big Data Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
+          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=afc93472e6a09eb2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Visualization Senior Associate - Home Lending Data &amp; Analytics</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athena, RDS, Scala, Polars, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6aec0750240018</t>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Python Engineer, Senior Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,46 +622,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9571f04802a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Ingeniero SR de Herramientas de Datos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Millicom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mora, LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,75 +706,390 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
+          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Solution Developer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c823da42c3926a3</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Advisor - Data Architect, Data Foundry</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Techster IT Services</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Application Support Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GCP Solution Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python / AWS)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Solution Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c823da42c3926a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Instacart</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D19" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
         </is>

--- a/results/job_matches_2026-06-15.xlsx
+++ b/results/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc93472e6a09eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ingeniero SR de Herramientas de Datos</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Millicom</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mora, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
+          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Ingeniero SR de Herramientas de Datos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Millicom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Mora, LA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,110 +986,985 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
+          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Solution Developer</t>
+          <t>Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c823da42c3926a3</t>
+          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Senior Software Engineer - Enterprise AI Products</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Advisor - Data Architect, Data Foundry</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Site AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Techster IT Services</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Big Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LiveRamp</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer - RFGL Systems</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>spire</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI / ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WPP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Application Support Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Tool / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IT - Developer II - IV (Remote)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Cincinnati Insurance Companies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SDET Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6636661aa7abd3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Neomax</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GCP Solution Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python / AWS)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer - Azure, Databricks</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-MFG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Instacart</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D44" t="n">
         <v>10.4</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
         </is>

--- a/results/job_matches_2026-06-15.xlsx
+++ b/results/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Python)</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=204e1619685f0b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b0a40d5ab0154f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Big Data Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
+          <t>https://www.indeed.com/viewjob?jk=af67504e645c60dd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Delivery Engineer - Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
+          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data/AI Engineer</t>
+          <t>Senior Big Data Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
+          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
+          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
+          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
+          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ingeniero SR de Herramientas de Datos</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Millicom</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mora, LA, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
+          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React)</t>
+          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise AI Products</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e28b9d0e31a69</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
+          <t>Ingeniero SR de Herramientas de Datos</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Millicom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Mora, LA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,49 +1126,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1191,37 +1191,37 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineering Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI / ML Platform Engineer</t>
+          <t>Senior Software Engineer - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
+          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Tool / Platform Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Techster IT Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SDET Consultant</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6636661aa7abd3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>WPP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Tool / Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+          <t>IT - Developer II - IV (Remote)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Cincinnati Insurance Companies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>SDET Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6636661aa7abd3c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,75 +1896,565 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-MFG</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Manufacturing Data Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hyosung</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36e3aebf070d07cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GCP Solution Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python / AWS)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BSA/AML &amp; Sanctions Data &amp; Modeling Support Analyst</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FlagStar Bank</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, Power BI, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87495ce263c1862</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer (Full-Stack / Backend / Frontend)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>REVIVE SOFTWARE SYSTEMS INC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde5a67a5251cda6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Texas General Land Office</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Engineer - Azure, Databricks</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-MFG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Instacart</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D58" t="n">
         <v>10.4</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
         </is>
